--- a/docs/d/85/inyear.xlsx
+++ b/docs/d/85/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 41 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 40 clubs short</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5503,8 +5503,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>1</v>
@@ -7229,8 +7229,8 @@
       <c r="T64" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U64" s="9" t="n">
-        <v>0</v>
+      <c r="U64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V64" s="10" t="n">
         <v>4</v>
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" s="9" t="n">
         <v>0</v>
@@ -10234,13 +10234,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>4</v>
       </c>
       <c r="W94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X94" s="10" t="n">
         <v>4</v>
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q97" s="9" t="n">
         <v>1</v>
@@ -10581,7 +10581,7 @@
         <v>0</v>
       </c>
       <c r="S97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T97" s="9" t="n">
         <v>0</v>
@@ -12322,7 +12322,7 @@
         <v>0</v>
       </c>
       <c r="S114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T114" s="9" t="n">
         <v>0</v>
@@ -13230,7 +13230,7 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>0</v>
@@ -14197,7 +14197,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14329,7 +14329,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/docs/d/85/inyear.xlsx
+++ b/docs/d/85/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,11 @@
       <c r="AB6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1743,7 +1747,11 @@
       <c r="AB10" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AC10" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2256,7 +2264,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2971,7 +2983,11 @@
       <c r="AB22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC22" s="4" t="inlineStr"/>
+      <c r="AC22" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3480,7 +3496,11 @@
       <c r="AB27" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC27" s="4" t="inlineStr"/>
+      <c r="AC27" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -3783,7 +3803,11 @@
       <c r="AB30" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC30" s="4" t="inlineStr"/>
+      <c r="AC30" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3884,7 +3908,11 @@
       <c r="AB31" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC31" s="4" t="inlineStr"/>
+      <c r="AC31" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -4288,7 +4316,11 @@
       <c r="AB35" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC35" s="4" t="inlineStr"/>
+      <c r="AC35" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -5205,7 +5237,11 @@
       <c r="AB44" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC44" s="4" t="inlineStr"/>
+      <c r="AC44" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -5306,7 +5342,11 @@
       <c r="AB45" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC45" s="4" t="inlineStr"/>
+      <c r="AC45" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -6021,7 +6061,11 @@
       <c r="AB52" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC52" s="4" t="inlineStr"/>
+      <c r="AC52" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6950,7 +6994,11 @@
       <c r="AB61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7253,7 +7301,11 @@
       <c r="AB64" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC64" s="4" t="inlineStr"/>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -7354,7 +7406,11 @@
       <c r="AB65" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC65" s="4" t="inlineStr"/>
+      <c r="AC65" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -7556,7 +7612,11 @@
       <c r="AB67" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC67" s="4" t="inlineStr"/>
+      <c r="AC67" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -7657,7 +7717,11 @@
       <c r="AB68" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC68" s="4" t="inlineStr"/>
+      <c r="AC68" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -8166,7 +8230,11 @@
       <c r="AB73" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC73" s="4" t="inlineStr"/>
+      <c r="AC73" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -8368,7 +8436,11 @@
       <c r="AB75" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC75" s="4" t="inlineStr"/>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8469,7 +8541,11 @@
       <c r="AB76" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC76" s="4" t="inlineStr"/>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -9790,7 +9866,11 @@
       <c r="AB89" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC89" s="4" t="inlineStr"/>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -11434,7 +11514,11 @@
       <c r="AB105" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC105" s="4" t="inlineStr"/>
+      <c r="AC105" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11943,7 +12027,11 @@
       <c r="AB110" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC110" s="4" t="inlineStr"/>
+      <c r="AC110" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -12145,7 +12233,11 @@
       <c r="AB112" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC112" s="4" t="inlineStr"/>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -13575,7 +13667,11 @@
       <c r="AB126" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC126" s="4" t="inlineStr"/>
+      <c r="AC126" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">

--- a/docs/d/85/inyear.xlsx
+++ b/docs/d/85/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 40 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 40 clubs short</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="P11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="9" t="n">
         <v>1</v>
@@ -3768,7 +3768,7 @@
         <v>2</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" s="9" t="n">
         <v>0</v>
@@ -3876,7 +3876,7 @@
         <v>2</v>
       </c>
       <c r="R31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="10" t="n">
         <v>2</v>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>1</v>
@@ -10966,7 +10966,7 @@
         <v>0</v>
       </c>
       <c r="Q100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R100" s="9" t="n">
         <v>0</v>
@@ -12154,7 +12154,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12206,8 +12206,8 @@
       <c r="S112" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T112" s="9" t="n">
-        <v>0</v>
+      <c r="T112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
@@ -12378,13 +12378,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -14821,7 +14821,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>

--- a/docs/d/85/inyear.xlsx
+++ b/docs/d/85/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 40 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 30 clubs short</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1299,8 +1299,8 @@
       <c r="P6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" s="9" t="n">
-        <v>1</v>
+      <c r="Q6" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R6" s="9" t="n">
         <v>0</v>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1948,8 +1948,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>1</v>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="P32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="9" t="n">
         <v>0</v>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4286,8 +4286,8 @@
       <c r="R35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S35" s="9" t="n">
-        <v>1</v>
+      <c r="S35" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T35" s="10" t="n">
         <v>1</v>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5745,8 +5745,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6367,8 +6367,8 @@
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="9" t="n">
-        <v>0</v>
+      <c r="Z55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7090,8 +7090,8 @@
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
@@ -8771,7 +8771,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8841,8 +8841,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -8911,7 +8911,7 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q80" s="9" t="n">
         <v>0</v>
@@ -8971,7 +8971,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9041,8 +9041,8 @@
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="9" t="n">
-        <v>0</v>
+      <c r="Z81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -9585,7 +9585,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9655,8 +9655,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>1</v>
@@ -10199,7 +10199,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10269,8 +10269,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -10405,7 +10405,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10475,8 +10475,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -12566,7 +12566,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12636,8 +12636,8 @@
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -13281,7 +13281,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13321,11 +13321,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P123" s="9" t="n">
-        <v>3</v>
+      <c r="P123" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
@@ -13963,7 +13963,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -14029,7 +14029,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -14194,7 +14194,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14359,7 +14359,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -14425,7 +14425,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14557,7 +14557,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14623,7 +14623,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14656,7 +14656,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14689,7 +14689,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14854,7 +14854,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -14887,7 +14887,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/docs/d/85/inyear.xlsx
+++ b/docs/d/85/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$129</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 30 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 30 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC128"/>
+  <dimension ref="A1:AC129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>4</v>
       </c>
       <c r="W4" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>4</v>
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>56</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1314,8 +1314,8 @@
       <c r="U6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="9" t="n">
-        <v>3</v>
+      <c r="V6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1577,17 +1577,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="8" t="n">
@@ -1682,17 +1682,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M10" s="8" t="n">
@@ -1787,17 +1787,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1892,13 +1892,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2199,13 +2199,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2304,17 +2304,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2409,13 +2409,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2611,13 +2611,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -3023,13 +3023,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3124,13 +3124,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>2</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3225,17 +3225,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M25" s="8" t="n">
@@ -3269,8 +3269,8 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>2</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3431,17 +3431,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3536,13 +3536,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3637,13 +3637,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3738,13 +3738,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3843,13 +3843,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>1</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3948,13 +3948,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -4049,13 +4049,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4194,11 +4194,11 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="9" t="n">
-        <v>0</v>
+      <c r="V34" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" s="9" t="n">
         <v>2</v>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4251,13 +4251,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4295,8 +4295,8 @@
       <c r="U35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="9" t="n">
-        <v>3</v>
+      <c r="V35" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4356,17 +4356,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M36" s="8" t="n">
@@ -4562,13 +4562,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4663,17 +4663,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>4</v>
       </c>
       <c r="W40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" s="10" t="n">
         <v>6</v>
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5071,13 +5071,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5172,13 +5172,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5204,8 +5204,8 @@
       <c r="Q44" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R44" s="9" t="n">
-        <v>1</v>
+      <c r="R44" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S44" s="9" t="n">
         <v>0</v>
@@ -5277,17 +5277,17 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M45" s="8" t="n">
@@ -5382,17 +5382,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5427,7 +5427,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5532,7 +5532,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5588,13 +5588,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5689,13 +5689,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -5790,13 +5790,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5996,13 +5996,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6101,17 +6101,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M53" s="8" t="n">
@@ -6206,13 +6206,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -6311,13 +6311,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6416,17 +6416,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6521,13 +6521,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6565,8 +6565,8 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>2</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6727,13 +6727,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6929,13 +6929,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>53</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>7</v>
+        <v>-13</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6976,8 +6976,8 @@
       <c r="V61" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W61" s="9" t="n">
-        <v>3</v>
+      <c r="W61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>6</v>
@@ -7079,7 +7079,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -7135,13 +7135,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7236,13 +7236,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>4</v>
       </c>
       <c r="W64" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X64" s="10" t="n">
         <v>4</v>
@@ -7341,13 +7341,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7446,17 +7446,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7490,11 +7490,11 @@
       <c r="U66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" s="9" t="n">
-        <v>0</v>
+      <c r="V66" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W66" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X66" s="10" t="n">
         <v>4</v>
@@ -7547,13 +7547,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7652,17 +7652,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7757,13 +7757,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -8165,17 +8165,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -8371,13 +8371,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8476,13 +8476,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>62</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8523,8 +8523,8 @@
       <c r="V76" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W76" s="9" t="n">
-        <v>2</v>
+      <c r="W76" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>7</v>
@@ -8581,17 +8581,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="8" t="n">
@@ -8686,13 +8686,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8884,13 +8884,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8985,17 +8985,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="8" t="n">
@@ -9030,7 +9030,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -9084,13 +9084,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -9288,13 +9288,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9393,13 +9393,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9494,17 +9494,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9539,7 +9539,7 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9599,17 +9599,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9801,13 +9801,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" s="9" t="n">
         <v>0</v>
@@ -9845,11 +9845,11 @@
       <c r="U89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>3</v>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>7</v>
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9906,13 +9906,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9950,8 +9950,8 @@
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="9" t="n">
-        <v>1</v>
+      <c r="V90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -10011,13 +10011,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10213,13 +10213,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -10314,17 +10314,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M94" s="8" t="n">
@@ -10419,13 +10419,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10520,17 +10520,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-19</v>
+      </c>
+      <c r="L96" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="8" t="n">
@@ -10625,17 +10625,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10670,7 +10670,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10730,13 +10730,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10835,13 +10835,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10936,13 +10936,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -10980,11 +10980,11 @@
       <c r="U100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V100" s="9" t="n">
-        <v>3</v>
+      <c r="V100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X100" s="10" t="n">
         <v>4</v>
@@ -11041,17 +11041,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -11086,7 +11086,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11124,11 +11124,11 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>28680481</v>
+        <v>28681029</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Shanghai Resonance Toastmasters Club</t>
+          <t>Shanghai AI Toastmasters Club</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -11146,10 +11146,10 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="K102" s="4" t="n">
         <v>0</v>
@@ -11197,20 +11197,18 @@
         <v>0</v>
       </c>
       <c r="X102" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z102" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB102" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB102" s="4" t="n"/>
       <c r="AC102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
@@ -11225,15 +11223,15 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>1490991</v>
+        <v>28680481</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Smart Speakers Shanghai</t>
+          <t>Shanghai Resonance Toastmasters Club</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11247,17 +11245,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L103" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -11274,10 +11272,10 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q103" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q103" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R103" s="9" t="n">
         <v>0</v>
@@ -11285,20 +11283,20 @@
       <c r="S103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T103" s="10" t="n">
-        <v>1</v>
+      <c r="T103" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
@@ -11310,7 +11308,7 @@
         <v>1</v>
       </c>
       <c r="AB103" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC103" s="4" t="inlineStr"/>
     </row>
@@ -11322,19 +11320,19 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>28680315</v>
+        <v>1490991</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>NXP Shanghai Toastmasters Club</t>
+          <t>Smart Speakers Shanghai</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11348,17 +11346,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -11375,10 +11373,10 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q104" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R104" s="9" t="n">
         <v>0</v>
@@ -11386,32 +11384,32 @@
       <c r="S104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T104" s="9" t="n">
-        <v>0</v>
+      <c r="T104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X104" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC104" s="4" t="inlineStr"/>
     </row>
@@ -11427,15 +11425,15 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>8698</v>
+        <v>28680315</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Pu Dong Toastmasters Club</t>
+          <t>NXP Shanghai Toastmasters Club</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11449,13 +11447,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11476,49 +11474,45 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q105" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q105" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S105" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T105" s="10" t="n">
-        <v>1</v>
+      <c r="S105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="W105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X105" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="10" t="n">
-        <v>1</v>
+      <c r="Z105" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB105" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC105" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11532,15 +11526,15 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>28679607</v>
+        <v>8698</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Shanghai Behind the Lens Toastmasters Club</t>
+          <t>Pu Dong Toastmasters Club</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11554,13 +11548,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11581,31 +11575,31 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q106" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" s="9" t="n">
-        <v>0</v>
+      <c r="S106" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X106" s="9" t="n">
-        <v>0</v>
+      <c r="X106" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
@@ -11617,9 +11611,13 @@
         <v>1</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC106" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -11633,15 +11631,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>1146944</v>
+        <v>28679607</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Shanghai L'espace-Temps Sino-Francophone Toastmasters Club</t>
+          <t>Shanghai Behind the Lens Toastmasters Club</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11655,13 +11653,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11700,49 +11698,49 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X107" s="10" t="n">
-        <v>5</v>
+      <c r="X107" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="9" t="n">
-        <v>0</v>
+      <c r="Z107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB107" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>7410811</v>
+        <v>1146944</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Be Being Better Toastmasters Club</t>
+          <t>Shanghai L'espace-Temps Sino-Francophone Toastmasters Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11756,17 +11754,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11792,40 +11790,36 @@
         <v>0</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T108" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T108" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB108" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X108" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z108" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA108" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB108" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC108" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+      <c r="AC108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -11839,15 +11833,15 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>28679795</v>
+        <v>7410811</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Chempartner Toastmasters Club</t>
+          <t>Be Being Better Toastmasters Club</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11861,13 +11855,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11897,36 +11891,40 @@
         <v>0</v>
       </c>
       <c r="S109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X109" s="9" t="n">
-        <v>2</v>
+      <c r="X109" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB109" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC109" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC109" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -11940,15 +11938,15 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>1737770</v>
+        <v>28679795</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Halo Psychology Toastmasters Club</t>
+          <t>Chempartner Toastmasters Club</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11962,17 +11960,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-36</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -12012,26 +12010,22 @@
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X110" s="10" t="n">
-        <v>6</v>
+      <c r="X110" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="10" t="n">
-        <v>1</v>
+      <c r="Z110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC110" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -12045,15 +12039,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>28680502</v>
+        <v>1737770</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Shanghai Influence Toastmasters Club</t>
+          <t>Halo Psychology Toastmasters Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12067,17 +12061,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -12118,21 +12112,25 @@
         <v>0</v>
       </c>
       <c r="X111" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB111" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC111" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC111" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -12142,19 +12140,19 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>996251</v>
+        <v>28680502</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>1st Bilingual Zhangjiang</t>
+          <t>Shanghai Influence Toastmasters Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12168,13 +12166,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12195,25 +12193,25 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q112" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S112" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T112" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -12224,20 +12222,16 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="10" t="n">
-        <v>1</v>
+      <c r="Z112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC112" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12251,15 +12245,15 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>4386750</v>
+        <v>996251</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>HUGS Toastmasters Club</t>
+          <t>1st Bilingual Zhangjiang</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12273,17 +12267,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L113" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -12300,22 +12294,22 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q113" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U113" s="9" t="n">
-        <v>0</v>
+      <c r="U113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V113" s="9" t="n">
         <v>2</v>
@@ -12336,11 +12330,11 @@
         <v>1</v>
       </c>
       <c r="AB113" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC113" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -12356,15 +12350,15 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>28678303</v>
+        <v>4386750</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Life Story Toastmasters Club</t>
+          <t>HUGS Toastmasters Club</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12378,13 +12372,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12414,10 +12408,10 @@
         <v>0</v>
       </c>
       <c r="S114" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T114" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U114" s="9" t="n">
         <v>0</v>
@@ -12441,9 +12435,13 @@
         <v>1</v>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC114" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC114" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -12457,11 +12455,11 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>7752843</v>
+        <v>28678303</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Showing &amp; Shining PMP Zhangjiang Toastmasters Club</t>
+          <t>Life Story Toastmasters Club</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
@@ -12479,13 +12477,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12515,7 +12513,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T115" s="9" t="n">
         <v>0</v>
@@ -12530,7 +12528,7 @@
         <v>0</v>
       </c>
       <c r="X115" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
@@ -12542,7 +12540,7 @@
         <v>1</v>
       </c>
       <c r="AB115" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AC115" s="4" t="inlineStr"/>
     </row>
@@ -12554,15 +12552,15 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>28675374</v>
+        <v>7752843</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Chemours China Toastmasters Club</t>
+          <t>Showing &amp; Shining PMP Zhangjiang Toastmasters Club</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
@@ -12580,13 +12578,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12625,13 +12623,13 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X116" s="9" t="n">
-        <v>0</v>
+      <c r="X116" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
@@ -12643,7 +12641,7 @@
         <v>1</v>
       </c>
       <c r="AB116" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC116" s="4" t="inlineStr"/>
     </row>
@@ -12659,15 +12657,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>6812069</v>
+        <v>28675374</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Marathon International Toastmasters Club</t>
+          <t>Chemours China Toastmasters Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12684,10 +12682,10 @@
         <v>14</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12726,25 +12724,25 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X117" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB117" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC117" s="4" t="inlineStr"/>
     </row>
@@ -12760,15 +12758,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>5042689</v>
+        <v>6812069</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>nToast</t>
+          <t>Marathon International Toastmasters Club</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12782,17 +12780,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12827,31 +12825,27 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X118" s="10" t="n">
-        <v>4</v>
+      <c r="X118" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="10" t="n">
-        <v>1</v>
+      <c r="Z118" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB118" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC118" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -12865,15 +12859,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>1936409</v>
+        <v>5042689</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>SHP Toastmasters</t>
+          <t>nToast</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12887,17 +12881,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L119" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
@@ -12913,11 +12907,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P119" s="10" t="n">
-        <v>5</v>
+      <c r="P119" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q119" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
@@ -12932,13 +12926,13 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X119" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
@@ -12950,11 +12944,11 @@
         <v>1</v>
       </c>
       <c r="AB119" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC119" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -12966,19 +12960,19 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>28680498</v>
+        <v>1936409</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Kistler Pudong Toastmasters Club</t>
+          <t>SHP Toastmasters</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12992,17 +12986,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L120" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="8" t="n">
@@ -13018,11 +13012,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P120" s="9" t="n">
-        <v>0</v>
+      <c r="P120" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" s="9" t="n">
         <v>0</v>
@@ -13037,27 +13031,31 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X120" s="9" t="n">
-        <v>0</v>
+      <c r="X120" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC120" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC120" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -13071,15 +13069,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>28677041</v>
+        <v>28680498</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Lingang Toastmasters Club</t>
+          <t>Kistler Pudong Toastmasters Club</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13093,17 +13091,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K121" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L121" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M121" s="8" t="n">
@@ -13143,20 +13141,20 @@
       <c r="W121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X121" s="10" t="n">
-        <v>4</v>
+      <c r="X121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="10" t="n">
-        <v>1</v>
+      <c r="Z121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB121" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC121" s="4" t="inlineStr"/>
     </row>
@@ -13172,11 +13170,11 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>28679854</v>
+        <v>28677041</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Shanghai Dishui Lake Chinese Toastmasters Club</t>
+          <t>Lingang Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
@@ -13194,17 +13192,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="8" t="n">
@@ -13239,7 +13237,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -13257,7 +13255,7 @@
         <v>1</v>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC122" s="4" t="inlineStr"/>
     </row>
@@ -13273,15 +13271,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>7961999</v>
+        <v>28679854</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Shanghai Nanhui Bilingual Toastmasters Club</t>
+          <t>Shanghai Dishui Lake Chinese Toastmasters Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13295,17 +13293,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M123" s="8" t="n">
@@ -13321,33 +13319,33 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P123" s="10" t="n">
+      <c r="P123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q123" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T123" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X123" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
@@ -13358,13 +13356,9 @@
         <v>1</v>
       </c>
       <c r="AB123" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC123" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -13374,19 +13368,19 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>28678851</v>
+        <v>7961999</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Harmony Toastmasters Club</t>
+          <t>Shanghai Nanhui Bilingual Toastmasters Club</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13400,17 +13394,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -13426,46 +13420,50 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P124" s="9" t="n">
-        <v>0</v>
+      <c r="P124" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X124" s="9" t="n">
-        <v>0</v>
+      <c r="X124" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB124" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC124" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC124" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -13479,15 +13477,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>7796643</v>
+        <v>28678851</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Manulife-Sinochem Toastmasters Club</t>
+          <t>Harmony Toastmasters Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13501,13 +13499,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13552,19 +13550,19 @@
         <v>0</v>
       </c>
       <c r="X125" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="10" t="n">
-        <v>1</v>
+      <c r="Z125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB125" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC125" s="4" t="inlineStr"/>
     </row>
@@ -13580,11 +13578,11 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>3945031</v>
+        <v>7796643</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Nexus China Toastmasters Club</t>
+          <t>Manulife-Sinochem Toastmasters Club</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
@@ -13602,17 +13600,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L126" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M126" s="8" t="n">
@@ -13647,31 +13645,27 @@
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X126" s="10" t="n">
-        <v>6</v>
+      <c r="X126" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z126" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC126" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -13685,15 +13679,15 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>28680476</v>
+        <v>3945031</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Shanghai Giraffe Toastmasters Club</t>
+          <t>Nexus China Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13707,17 +13701,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M127" s="8" t="n">
@@ -13734,7 +13728,7 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q127" s="9" t="n">
         <v>0</v>
@@ -13745,34 +13739,38 @@
       <c r="S127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T127" s="10" t="n">
-        <v>1</v>
+      <c r="T127" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X127" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z127" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB127" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC127" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC127" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -13786,15 +13784,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>28680531</v>
+        <v>28680476</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Shanghai Professional Speakers Toastmasters Club</t>
+          <t>Shanghai Giraffe Toastmasters Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13808,10 +13806,10 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K128" s="4" t="n">
         <v>0</v>
@@ -13835,7 +13833,7 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q128" s="9" t="n">
         <v>0</v>
@@ -13846,8 +13844,8 @@
       <c r="S128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T128" s="9" t="n">
-        <v>0</v>
+      <c r="T128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U128" s="9" t="n">
         <v>0</v>
@@ -13858,8 +13856,8 @@
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X128" s="9" t="n">
-        <v>1</v>
+      <c r="X128" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
@@ -13875,8 +13873,109 @@
       </c>
       <c r="AC128" s="4" t="inlineStr"/>
     </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="n">
+        <v>28680531</v>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>Shanghai Professional Speakers Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G129" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I129" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J129" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K129" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M129" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O129" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA129" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC129" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC128"/>
+  <autoFilter ref="A1:AC129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13963,13 +14062,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -14011,7 +14110,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -14044,7 +14143,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -14077,7 +14176,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -14128,7 +14227,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -14143,7 +14242,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -14194,7 +14293,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -14209,7 +14308,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -14242,7 +14341,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -14260,7 +14359,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14275,7 +14374,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -14308,7 +14407,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14341,7 +14440,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -14359,7 +14458,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -14374,7 +14473,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -14392,7 +14491,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -14458,7 +14557,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14506,7 +14605,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -14524,7 +14623,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14539,7 +14638,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -14572,7 +14671,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -14605,7 +14704,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -14623,7 +14722,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14638,7 +14737,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -14671,7 +14770,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -14704,7 +14803,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -14719,16 +14818,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -14770,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -14803,7 +14902,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -14821,7 +14920,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -14902,7 +15001,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -14935,7 +15034,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/85/inyear.xlsx
+++ b/docs/d/85/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/85/inyear.xlsx
+++ b/docs/d/85/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/85/inyear.xlsx
+++ b/docs/d/85/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/85/inyear.xlsx
+++ b/docs/d/85/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/85/inyear.xlsx
+++ b/docs/d/85/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 30 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 30 clubs short</t>
         </is>
       </c>
     </row>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>4</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>5</v>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="P22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>0</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3124,13 +3124,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3168,8 +3168,8 @@
       <c r="U24" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V24" s="9" t="n">
-        <v>3</v>
+      <c r="V24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -4804,7 +4804,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T40" s="9" t="n">
         <v>0</v>
@@ -4948,11 +4948,11 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>28677343</v>
+        <v>28677093</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Entrepreneurs Toastmasters Shanghai</t>
+          <t>FedEx Shanghai Growing Toastmasters Club</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
@@ -4973,10 +4973,10 @@
         <v>0</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>1</v>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC42" s="4" t="inlineStr"/>
     </row>
@@ -5049,15 +5049,15 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>28677093</v>
+        <v>28678347</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>FedEx Shanghai Growing Toastmasters Club</t>
+          <t>FIRE Toastmasters Club</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5071,17 +5071,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L43" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M43" s="8" t="n">
@@ -5098,13 +5098,13 @@
         </is>
       </c>
       <c r="P43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q43" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R43" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S43" s="9" t="n">
         <v>0</v>
@@ -5116,27 +5116,31 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X43" s="9" t="n">
-        <v>0</v>
+      <c r="X43" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB43" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC43" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC43" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -5150,15 +5154,15 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>28678347</v>
+        <v>5038826</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>FIRE Toastmasters Club</t>
+          <t>Shanghai IMAGINE Toastmasters Club</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5172,17 +5176,17 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M44" s="8" t="n">
@@ -5199,31 +5203,31 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q44" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R44" s="10" t="n">
-        <v>2</v>
+      <c r="Q44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T44" s="9" t="n">
-        <v>0</v>
+      <c r="T44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X44" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y44" s="9" t="n">
         <v>0</v>
@@ -5255,15 +5259,15 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>5038826</v>
+        <v>28677343</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Shanghai IMAGINE Toastmasters Club</t>
+          <t>Shanghai OPC Bilingual Toastmasters Club</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5277,13 +5281,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5304,7 +5308,7 @@
         </is>
       </c>
       <c r="P45" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="9" t="n">
         <v>0</v>
@@ -5315,38 +5319,34 @@
       <c r="S45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T45" s="10" t="n">
-        <v>1</v>
+      <c r="T45" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X45" s="10" t="n">
-        <v>5</v>
+      <c r="X45" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="10" t="n">
-        <v>1</v>
+      <c r="Z45" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA45" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB45" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC45" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5382,17 +5382,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L46" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5426,11 +5426,11 @@
       <c r="U46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="9" t="n">
-        <v>1</v>
+      <c r="V46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X46" s="10" t="n">
         <v>4</v>
@@ -6959,7 +6959,7 @@
         <v>4</v>
       </c>
       <c r="Q61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" s="9" t="n">
         <v>0</v>
@@ -8064,13 +8064,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8371,13 +8371,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8415,8 +8415,8 @@
       <c r="U75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V75" s="9" t="n">
-        <v>2</v>
+      <c r="V75" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>62</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>4</v>
       </c>
       <c r="W76" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>7</v>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8686,13 +8686,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8730,8 +8730,8 @@
       <c r="U78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V78" s="9" t="n">
-        <v>2</v>
+      <c r="V78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8911,7 +8911,7 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q80" s="9" t="n">
         <v>0</v>
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9801,13 +9801,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>7</v>
@@ -10716,7 +10716,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10730,13 +10730,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10774,11 +10774,11 @@
       <c r="U98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="9" t="n">
-        <v>3</v>
+      <c r="V98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>5</v>
@@ -10922,7 +10922,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10972,10 +10972,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U100" s="9" t="n">
         <v>0</v>
@@ -12061,13 +12061,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -12309,7 +12309,7 @@
         <v>1</v>
       </c>
       <c r="U113" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V113" s="9" t="n">
         <v>2</v>
@@ -12911,7 +12911,7 @@
         <v>0</v>
       </c>
       <c r="Q119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
@@ -12986,13 +12986,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -13380,7 +13380,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13435,8 +13435,8 @@
       <c r="T124" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U124" s="9" t="n">
-        <v>0</v>
+      <c r="U124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V124" s="9" t="n">
         <v>3</v>
@@ -14227,7 +14227,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -14392,7 +14392,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14407,7 +14407,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -14623,7 +14623,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14656,7 +14656,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14788,7 +14788,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14821,7 +14821,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -14986,7 +14986,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/docs/d/85/inyear.xlsx
+++ b/docs/d/85/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 30 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 30 clubs short</t>
         </is>
       </c>
     </row>
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>56</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="R6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="10" t="n">
         <v>2</v>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="P15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>1</v>
@@ -2240,8 +2240,8 @@
       <c r="T15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U15" s="9" t="n">
-        <v>0</v>
+      <c r="U15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V15" s="9" t="n">
         <v>1</v>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>0</v>
@@ -4461,13 +4461,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -5176,13 +5176,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5325,8 +5325,8 @@
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="9" t="n">
-        <v>3</v>
+      <c r="V45" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -7135,13 +7135,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7278,7 +7278,7 @@
         <v>1</v>
       </c>
       <c r="U64" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V64" s="10" t="n">
         <v>4</v>
@@ -8462,7 +8462,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8514,8 +8514,8 @@
       <c r="S76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="9" t="n">
-        <v>0</v>
+      <c r="T76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U76" s="9" t="n">
         <v>0</v>
@@ -8985,13 +8985,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11899,8 +11899,8 @@
       <c r="U109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V109" s="9" t="n">
-        <v>3</v>
+      <c r="V109" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11960,13 +11960,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-36</v>
+        <v>-28</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12267,13 +12267,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12293,14 +12293,14 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P113" s="9" t="n">
-        <v>3</v>
+      <c r="P113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q113" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R113" s="9" t="n">
-        <v>1</v>
+      <c r="R113" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S113" s="9" t="n">
         <v>1</v>
@@ -12312,7 +12312,7 @@
         <v>2</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12477,13 +12477,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>1</v>
       </c>
       <c r="U124" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V124" s="9" t="n">
         <v>3</v>
@@ -14161,7 +14161,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -14359,7 +14359,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14623,13 +14623,13 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -14887,7 +14887,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -14920,13 +14920,13 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
